--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CARBURADOR - 19_01 A.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CARBURADOR - 19_01 A.xlsx
@@ -482,7 +482,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -578,7 +582,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -599,7 +607,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -645,7 +657,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CARBURADOR - 19_01 A.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CARBURADOR - 19_01 A.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t> </t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,67 +652,262 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>25</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>40</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
